--- a/diseases/d122/2020-2025.xlsx
+++ b/diseases/d122/2020-2025.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2101,9 +2092,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2497,9 +2485,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2893,9 +2878,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3289,9 +3271,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3685,9 +3664,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4081,9 +4057,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4477,9 +4450,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4873,9 +4843,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5269,9 +5236,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5665,9 +5629,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6209,9 +6170,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6605,9 +6563,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7001,9 +6956,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7397,9 +7349,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7793,9 +7742,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8189,9 +8135,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8585,9 +8528,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8981,9 +8921,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9377,9 +9314,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9921,9 +9855,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -10317,9 +10248,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10713,9 +10641,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -11109,9 +11034,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11653,9 +11575,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -12641,9 +12560,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -13629,9 +13545,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -14617,9 +14530,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15753,9 +15663,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16741,9 +16648,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17729,9 +17633,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -18865,9 +18766,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19853,9 +19751,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20841,9 +20736,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -21977,9 +21869,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -22965,9 +22854,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -24249,9 +24135,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -25237,9 +25120,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -26225,9 +26105,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -27213,9 +27090,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -28349,9 +28223,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -29337,9 +29208,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30325,9 +30193,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -31461,9 +31326,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -32449,9 +32311,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -33585,9 +33444,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -34573,9 +34429,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -35561,9 +35414,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -36697,9 +36547,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -36845,9 +36692,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -37833,9 +37677,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -38821,9 +38662,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -39957,9 +39795,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -40945,9 +40780,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -41933,9 +41765,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -43069,9 +42898,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -44057,9 +43883,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -45193,9 +45016,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -46181,9 +46001,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -47169,9 +46986,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -48305,9 +48119,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -49293,9 +49104,6 @@
       <c r="O288" t="n">
         <v>1</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.01115149501123931</v>
       </c>
@@ -49441,9 +49249,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -50429,9 +50234,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -51417,9 +51219,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -52553,9 +52352,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -53541,9 +53337,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -54677,9 +54470,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -55665,9 +55455,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -56653,9 +56440,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -57789,9 +57573,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -58777,9 +58558,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -59765,9 +59543,6 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0</v>
       </c>
@@ -60899,9 +60674,6 @@
         <v>0</v>
       </c>
       <c r="O359" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q359" t="n">
         <v>0</v>
       </c>
       <c r="R359" t="n">
